--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487628_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487628_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.1321</v>
+        <v>4.8111</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3673</v>
+        <v>6.8283</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.2352</v>
+        <v>-2.0172</v>
       </c>
       <c r="G2" t="n">
         <v>5.0203</v>
@@ -610,13 +610,13 @@
         <v>1.1642</v>
       </c>
       <c r="S2" t="n">
-        <v>0.17</v>
+        <v>0.849</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1806</v>
+        <v>0.2804</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3506</v>
+        <v>0.5687</v>
       </c>
       <c r="V2" t="n">
         <v>-0.2821</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7757</v>
+        <v>4.4397</v>
       </c>
       <c r="E3" t="n">
-        <v>3.0174</v>
+        <v>3.5179</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7583</v>
+        <v>0.9218</v>
       </c>
       <c r="G3" t="n">
         <v>2.3965</v>
@@ -688,13 +688,13 @@
         <v>1.7463</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.08500000000000001</v>
+        <v>0.579</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0011</v>
+        <v>0.5016</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0861</v>
+        <v>0.0774</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2821</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. GUEYE</t>
+          <t>E. LLACER SIMLAT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.4235</v>
+        <v>2.728</v>
       </c>
       <c r="E4" t="n">
-        <v>5.4018</v>
+        <v>0.9567</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.9783</v>
+        <v>1.7713</v>
       </c>
       <c r="G4" t="n">
-        <v>4.7364</v>
+        <v>1.0317</v>
       </c>
       <c r="H4" t="n">
-        <v>1.0949</v>
+        <v>-1.1839</v>
       </c>
       <c r="I4" t="n">
-        <v>3.6415</v>
+        <v>2.2156</v>
       </c>
       <c r="J4" t="n">
-        <v>5.8841</v>
+        <v>0.5718</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2204</v>
+        <v>-1.4047</v>
       </c>
       <c r="L4" t="n">
-        <v>3.6638</v>
+        <v>1.9765</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.1477</v>
+        <v>0.4599</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1254</v>
+        <v>0.2208</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.0223</v>
+        <v>0.2391</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.9403</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q4" t="n">
         <v>-2.9105</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9702</v>
+        <v>1.7463</v>
       </c>
       <c r="S4" t="n">
-        <v>3.687</v>
+        <v>1.6367</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4282</v>
+        <v>0.8476</v>
       </c>
       <c r="U4" t="n">
-        <v>1.2589</v>
+        <v>0.7891</v>
       </c>
       <c r="V4" t="n">
-        <v>-3.0597</v>
+        <v>1.2239</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.0597</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. LLACER SIMLAT</t>
+          <t>K. SKUTYELNIK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.564</v>
+        <v>1.8169</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6564</v>
+        <v>1.3932</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9076</v>
+        <v>0.4237</v>
       </c>
       <c r="G5" t="n">
-        <v>1.0317</v>
+        <v>-2.074</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.1839</v>
+        <v>-1.6675</v>
       </c>
       <c r="I5" t="n">
-        <v>2.2156</v>
+        <v>-0.4065</v>
       </c>
       <c r="J5" t="n">
-        <v>0.5718</v>
+        <v>-1.5438</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.4047</v>
+        <v>-0.8815</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9765</v>
+        <v>-0.6623</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4599</v>
+        <v>-0.5302</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2208</v>
+        <v>-0.786</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2391</v>
+        <v>0.2558</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.1642</v>
+        <v>1.3582</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9105</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7463</v>
+        <v>1.3582</v>
       </c>
       <c r="S5" t="n">
-        <v>1.4726</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.5473</v>
+        <v>0.4893</v>
       </c>
       <c r="U5" t="n">
-        <v>0.9253</v>
+        <v>-0.4043</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2239</v>
+        <v>2.4477</v>
       </c>
       <c r="W5" t="n">
         <v>2.4477</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>K. SKUTYELNIK</t>
+          <t>S. GUEYE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.9809</v>
+        <v>1.5921</v>
       </c>
       <c r="E6" t="n">
-        <v>1.6935</v>
+        <v>4.061</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2874</v>
+        <v>-2.4689</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.074</v>
+        <v>4.7364</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.6675</v>
+        <v>1.0949</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.4065</v>
+        <v>3.6415</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.5438</v>
+        <v>5.8841</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.8815</v>
+        <v>2.2204</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6623</v>
+        <v>3.6638</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5302</v>
+        <v>-1.1477</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.786</v>
+        <v>-1.1254</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2558</v>
+        <v>-0.0223</v>
       </c>
       <c r="P6" t="n">
-        <v>1.3582</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q6" t="n">
+        <v>-2.9105</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.9702</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.8556</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.0873</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.7683</v>
+      </c>
+      <c r="V6" t="n">
+        <v>-3.0597</v>
+      </c>
+      <c r="W6" t="n">
         <v>0</v>
       </c>
-      <c r="R6" t="n">
-        <v>1.3582</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.249</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0.7896</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.5406</v>
-      </c>
-      <c r="V6" t="n">
-        <v>2.4477</v>
-      </c>
-      <c r="W6" t="n">
-        <v>2.4477</v>
-      </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-3.0597</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>V. ESPAÑOL BERENGUER</t>
+          <t>D. VIERA LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1194</v>
+        <v>0.222</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0012</v>
+        <v>0.7436</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1206</v>
+        <v>-0.5216</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.4832</v>
+        <v>-0.1217</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0618</v>
+        <v>0.1442</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.545</v>
+        <v>-0.2659</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0618</v>
+        <v>0.6196</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0618</v>
+        <v>0.4573</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.1624</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.545</v>
+        <v>-0.7413</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-0.3131</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.545</v>
+        <v>-0.4282</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3881</v>
+        <v>1.3582</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0242</v>
+        <v>0.8213</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0606</v>
+        <v>0.5016</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0363</v>
+        <v>0.3197</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.8358</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3776</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.4582</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>D. VIERA LOPEZ</t>
+          <t>V. ESPAÑOL BERENGUER</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.224</v>
+        <v>-0.0649</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2431</v>
+        <v>0.0012</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4671</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.1217</v>
+        <v>-0.4832</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1442</v>
+        <v>0.0618</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2659</v>
+        <v>-0.545</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6196</v>
+        <v>0.0618</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4573</v>
+        <v>0.0618</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1624</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.7413</v>
+        <v>-0.545</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.3131</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4282</v>
+        <v>-0.545</v>
       </c>
       <c r="P8" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.3582</v>
+        <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3753</v>
+        <v>0.0303</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0011</v>
+        <v>-0.0606</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3742</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.8358</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3776</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.4582</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2672</v>
+        <v>-0.7711</v>
       </c>
       <c r="E9" t="n">
-        <v>2.2334</v>
+        <v>1.5932</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.5006</v>
+        <v>-2.3643</v>
       </c>
       <c r="G9" t="n">
         <v>-1.2541</v>
@@ -1156,13 +1156,13 @@
         <v>0.9702</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3465</v>
+        <v>-0.1573</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7896</v>
+        <v>0.1494</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.443</v>
+        <v>-0.3067</v>
       </c>
       <c r="V9" t="n">
         <v>-0.3299</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0701</v>
+        <v>-1.7999</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8218</v>
+        <v>-0.3608</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2483</v>
+        <v>-1.4391</v>
       </c>
       <c r="G10" t="n">
         <v>-3.0205</v>
@@ -1234,13 +1234,13 @@
         <v>1.9403</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4794</v>
+        <v>-0.2092</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3623</v>
+        <v>0.0987</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1171</v>
+        <v>-0.3078</v>
       </c>
       <c r="V10" t="n">
         <v>2.4</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9501</v>
+        <v>-3.4257</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.4773</v>
+        <v>-4.1164</v>
       </c>
       <c r="F11" t="n">
-        <v>0.5272</v>
+        <v>0.6907</v>
       </c>
       <c r="G11" t="n">
         <v>-3.7833</v>
@@ -1312,13 +1312,13 @@
         <v>0.9702</v>
       </c>
       <c r="S11" t="n">
-        <v>0.4735</v>
+        <v>0.9979</v>
       </c>
       <c r="T11" t="n">
-        <v>0.4262</v>
+        <v>0.787</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0474</v>
+        <v>0.2109</v>
       </c>
       <c r="V11" t="n">
         <v>0.3299</v>
@@ -1345,22 +1345,22 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.2454</v>
+        <v>9.548200000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>14.315</v>
+        <v>14.6179</v>
       </c>
       <c r="F12" t="n">
-        <v>-5.0696</v>
+        <v>-5.069699999999999</v>
       </c>
       <c r="G12" t="n">
         <v>2.448099999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>1.029900000000001</v>
+        <v>1.0299</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4182</v>
+        <v>1.418200000000001</v>
       </c>
       <c r="J12" t="n">
         <v>13.2299</v>
@@ -1378,10 +1378,10 @@
         <v>-9.919500000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.8621000000000002</v>
+        <v>-0.8621</v>
       </c>
       <c r="P12" t="n">
-        <v>4.440892098500626e-16</v>
+        <v>2.220446049250313e-16</v>
       </c>
       <c r="Q12" t="n">
         <v>-12.6121</v>
@@ -1390,16 +1390,16 @@
         <v>12.6122</v>
       </c>
       <c r="S12" t="n">
-        <v>6.185299999999999</v>
+        <v>6.488300000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>4.3796</v>
+        <v>4.6823</v>
       </c>
       <c r="U12" t="n">
-        <v>1.8059</v>
+        <v>1.8061</v>
       </c>
       <c r="V12" t="n">
-        <v>0.6119000000000001</v>
+        <v>0.6118999999999997</v>
       </c>
       <c r="W12" t="n">
         <v>9.3178</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.1594</v>
+        <v>3.2135</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1938</v>
+        <v>3.4931</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0344</v>
+        <v>-0.2797</v>
       </c>
       <c r="G13" t="n">
         <v>3.8998</v>
@@ -1468,13 +1468,13 @@
         <v>2.1344</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1516</v>
+        <v>-0.7944</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6695</v>
+        <v>-0.0312</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5179</v>
+        <v>-0.7632</v>
       </c>
       <c r="V13" t="n">
         <v>-0.08599999999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.5128</v>
+        <v>0.1512</v>
       </c>
       <c r="E14" t="n">
-        <v>3.2877</v>
+        <v>3.7882</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.8005</v>
+        <v>-3.637</v>
       </c>
       <c r="G14" t="n">
         <v>2.4941</v>
@@ -1546,13 +1546,13 @@
         <v>1.7463</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.589</v>
+        <v>-0.925</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8962</v>
+        <v>-0.3957</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6929</v>
+        <v>-0.5293</v>
       </c>
       <c r="V14" t="n">
         <v>-1.2239</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.5929</v>
+        <v>-0.4745</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7933</v>
+        <v>0.9935</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.3862</v>
+        <v>-1.4679</v>
       </c>
       <c r="G15" t="n">
         <v>-0.2033</v>
@@ -1624,13 +1624,13 @@
         <v>0.7761</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8552999999999999</v>
+        <v>-0.7369</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6662</v>
+        <v>-0.466</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1891</v>
+        <v>-0.2708</v>
       </c>
       <c r="V15" t="n">
         <v>0.6597</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C. CUESTA DE SANTOS</t>
+          <t>A. OLMEDO VELASCO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.8041</v>
+        <v>-1.2894</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9372</v>
+        <v>0.2464</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.7413</v>
+        <v>-1.5358</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.1076</v>
+        <v>-2.5049</v>
       </c>
       <c r="H16" t="n">
-        <v>0.0198</v>
+        <v>-2.2162</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1274</v>
+        <v>-0.2887</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.1667</v>
+        <v>-0.1374</v>
       </c>
       <c r="K16" t="n">
-        <v>1.1452</v>
+        <v>-0.3048</v>
       </c>
       <c r="L16" t="n">
-        <v>-1.3118</v>
+        <v>0.1674</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0591</v>
+        <v>-2.3675</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1254</v>
+        <v>-1.9114</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1845</v>
+        <v>-0.4561</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9702</v>
+        <v>1.3582</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9702</v>
+        <v>2.3284</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.8309</v>
+        <v>-1.6582</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.12</v>
+        <v>-0.4341</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.7108</v>
+        <v>-1.2242</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.8358</v>
+        <v>1.5155</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2239</v>
+        <v>1.788</v>
       </c>
       <c r="X16" t="n">
-        <v>-3.0597</v>
+        <v>-0.2725</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. PEREZ BERNABEU</t>
+          <t>C. CUESTA DE SANTOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.9669</v>
+        <v>-1.8769</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.8309</v>
+        <v>0.8371</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.136</v>
+        <v>-2.714</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.8848</v>
+        <v>-0.1076</v>
       </c>
       <c r="H17" t="n">
-        <v>0.636</v>
+        <v>0.0198</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.5208</v>
+        <v>-0.1274</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.5259</v>
+        <v>-0.1667</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0216</v>
+        <v>1.1452</v>
       </c>
       <c r="L17" t="n">
-        <v>-2.5475</v>
+        <v>-1.3118</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.3588</v>
+        <v>0.0591</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3856</v>
+        <v>-1.1254</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.9733000000000001</v>
+        <v>1.1845</v>
       </c>
       <c r="P17" t="n">
-        <v>0.194</v>
+        <v>0.9702</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1023</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.2288</v>
+        <v>-0.2201</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3311</v>
+        <v>-0.6836</v>
       </c>
       <c r="V17" t="n">
-        <v>0.6215000000000001</v>
+        <v>-1.8358</v>
       </c>
       <c r="W17" t="n">
-        <v>0.894</v>
+        <v>1.2239</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2725</v>
+        <v>-3.0597</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>A. OLMEDO VELASCO</t>
+          <t>A. GOMEZ SERRANO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.0986</v>
+        <v>-2.1065</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.154</v>
+        <v>-0.2901</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9446</v>
+        <v>-1.8164</v>
       </c>
       <c r="G18" t="n">
-        <v>-2.5049</v>
+        <v>-2.5335</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.2162</v>
+        <v>-1.146</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2887</v>
+        <v>-1.3875</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.1374</v>
+        <v>-0.6292</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.3048</v>
+        <v>-0.482</v>
       </c>
       <c r="L18" t="n">
-        <v>0.1674</v>
+        <v>-0.1473</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3675</v>
+        <v>-1.9042</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.9114</v>
+        <v>-0.6641</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.4561</v>
+        <v>-1.2402</v>
       </c>
       <c r="P18" t="n">
-        <v>1.3582</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R18" t="n">
-        <v>2.3284</v>
+        <v>1.5523</v>
       </c>
       <c r="S18" t="n">
-        <v>-2.4675</v>
+        <v>-0.4183</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.8345</v>
+        <v>-0.1683</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.633</v>
+        <v>-0.2501</v>
       </c>
       <c r="V18" t="n">
-        <v>1.5155</v>
+        <v>1.2334</v>
       </c>
       <c r="W18" t="n">
-        <v>1.788</v>
+        <v>2.4477</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2725</v>
+        <v>-1.2143</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GOMEZ SERRANO</t>
+          <t>E. PEREZ BERNABEU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.379</v>
+        <v>-2.4848</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2901</v>
+        <v>-1.8309</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0889</v>
+        <v>-0.6539</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5335</v>
+        <v>-2.8848</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.146</v>
+        <v>0.636</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3875</v>
+        <v>-3.5208</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6292</v>
+        <v>-1.5259</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.482</v>
+        <v>1.0216</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.1473</v>
+        <v>-2.5475</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.9042</v>
+        <v>-1.3588</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6641</v>
+        <v>-0.3856</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.2402</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.3881</v>
+        <v>0.194</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6909</v>
+        <v>-0.4155</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.1683</v>
+        <v>-0.2288</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5226</v>
+        <v>-0.1867</v>
       </c>
       <c r="V19" t="n">
-        <v>1.2334</v>
+        <v>0.6215000000000001</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4477</v>
+        <v>0.894</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2143</v>
+        <v>-0.2725</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.0505</v>
+        <v>-4.3781</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.8674</v>
+        <v>-2.1677</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1831</v>
+        <v>-2.2104</v>
       </c>
       <c r="G20" t="n">
         <v>-0.608</v>
@@ -2014,13 +2014,13 @@
         <v>1.9403</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0058</v>
+        <v>-0.3334</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4385</v>
+        <v>0.1382</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4443</v>
+        <v>-0.4716</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4964</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-9.245400000000002</v>
+        <v>-9.2455</v>
       </c>
       <c r="E21" t="n">
         <v>5.0696</v>
       </c>
       <c r="F21" t="n">
-        <v>-14.315</v>
+        <v>-14.3151</v>
       </c>
       <c r="G21" t="n">
         <v>-2.4482</v>
@@ -2062,7 +2062,7 @@
         <v>-1.0297</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.4183</v>
+        <v>-1.418299999999999</v>
       </c>
       <c r="J21" t="n">
         <v>10.7818</v>
@@ -2071,7 +2071,7 @@
         <v>9.9194</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8624000000000001</v>
+        <v>0.8623999999999992</v>
       </c>
       <c r="M21" t="n">
         <v>-13.2298</v>
@@ -2083,7 +2083,7 @@
         <v>-2.2806</v>
       </c>
       <c r="P21" t="n">
-        <v>2.220446049250313e-16</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
         <v>-12.6121</v>
@@ -2092,16 +2092,16 @@
         <v>12.6122</v>
       </c>
       <c r="S21" t="n">
-        <v>-6.185499999999999</v>
+        <v>-6.1854</v>
       </c>
       <c r="T21" t="n">
         <v>-1.806</v>
       </c>
       <c r="U21" t="n">
-        <v>-4.379499999999999</v>
+        <v>-4.3795</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6120000000000001</v>
+        <v>-0.6119999999999999</v>
       </c>
       <c r="W21" t="n">
         <v>8.7059</v>
